--- a/Proj1_control_signals.xlsx
+++ b/Proj1_control_signals.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="74">
   <si>
     <t xml:space="preserve">Instruction</t>
   </si>
@@ -28,143 +28,220 @@
     <t xml:space="preserve">Opcode (Binary)</t>
   </si>
   <si>
-    <t xml:space="preserve">Funct 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funct 7</t>
+    <t xml:space="preserve">Funct3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funct7</t>
   </si>
   <si>
     <t xml:space="preserve">Control Signals</t>
   </si>
   <si>
-    <t xml:space="preserve">ALUSrc 1 bit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALUControl 4 bit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ImmType 2 bits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andlink</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MemWrite </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[MemWrite from register]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RegWrite </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1 bit</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">MemtoReg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MemRead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jump</t>
+    <t xml:space="preserve">ALUSrc (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALUControl (4 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ImmType (2 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AndLink (2 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MemWrite (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RegWrite (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MemToReg (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MemRead (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branch (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jump (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALU_Or_Imm_Jump (1 bit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag_Mux (2 bits)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag_Or_Nflag</t>
   </si>
   <si>
     <t xml:space="preserve">addi</t>
   </si>
   <si>
-    <t xml:space="preserve">"0010011"</t>
+    <t xml:space="preserve">0010011</t>
   </si>
   <si>
     <t xml:space="preserve">000</t>
   </si>
   <si>
-    <t xml:space="preserve">xxxxxxxx</t>
+    <t xml:space="preserve">XXXXXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0110011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">andi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0110111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
   </si>
   <si>
     <t xml:space="preserve">0010</t>
   </si>
   <si>
-    <t xml:space="preserve">01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">add</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“0110011”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">andi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“0010011”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">“0110111”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">xxx</t>
+    <t xml:space="preserve">xori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sltiu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">srl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0100000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0100011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1100011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XX?</t>
   </si>
 </sst>
 </file>
@@ -175,7 +252,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -197,14 +274,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -271,7 +340,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -291,7 +360,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultColWidth="10.86328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.88"/>
@@ -307,8 +376,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="15.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="20.01"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="16" style="2" width="10.87"/>
   </cols>
   <sheetData>
@@ -363,7 +432,7 @@
       <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -375,196 +444,1078 @@
       <c r="N2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P23" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/Proj1_control_signals.xlsx
+++ b/Proj1_control_signals.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="91">
   <si>
     <t xml:space="preserve">Instruction</t>
   </si>
@@ -242,6 +242,57 @@
   </si>
   <si>
     <t xml:space="preserve">XX?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bltu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bgeu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jalr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lbu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lhu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">srli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">srai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auipc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wfi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????</t>
   </si>
 </sst>
 </file>
@@ -276,12 +327,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -318,7 +375,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -343,6 +400,22 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -360,7 +433,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="10.86328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.88"/>
@@ -1515,7 +1588,759 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P23" s="1"/>
+      <c r="A23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>1101111</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1100111</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>101</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>110011</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>10011</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>10011</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>10111</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="9"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
